--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -413,28 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="C1" t="inlineStr">
         <is>
-          <t>Distance 1</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Distance 2</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Angle</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -446,20 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fiducial 1</t>
+          <t>Pad Pos 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>121.37971</v>
+        <v>16.73925</v>
       </c>
       <c r="D2" t="n">
-        <v>86.01401</v>
+        <v>16.62807</v>
       </c>
       <c r="E2" t="n">
-        <v>91.00273</v>
+        <v>16.72936</v>
       </c>
       <c r="F2" t="n">
-        <v>508.74797</v>
+        <v>42.33337</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0512</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.78314</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>121.10178</v>
+        <v>16.77037</v>
       </c>
       <c r="D3" t="n">
-        <v>85.81307</v>
+        <v>16.30489</v>
       </c>
       <c r="E3" t="n">
-        <v>91.31447</v>
+        <v>16.55901</v>
       </c>
       <c r="F3" t="n">
-        <v>518.77864</v>
+        <v>42.86088</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.05026</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.8589</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>120.79294</v>
+        <v>16.48915</v>
       </c>
       <c r="D4" t="n">
-        <v>86.20941000000001</v>
+        <v>16.30932</v>
       </c>
       <c r="E4" t="n">
-        <v>90.99353000000001</v>
+        <v>16.45169</v>
       </c>
       <c r="F4" t="n">
-        <v>517.33173</v>
+        <v>42.57682</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.05179</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.80536</v>
       </c>
     </row>
     <row r="5">
@@ -507,16 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>121.26715</v>
+        <v>16.85762</v>
       </c>
       <c r="D5" t="n">
-        <v>86.07823</v>
+        <v>16.60748</v>
       </c>
       <c r="E5" t="n">
-        <v>90.40721000000001</v>
+        <v>16.65958</v>
       </c>
       <c r="F5" t="n">
-        <v>518.70048</v>
+        <v>42.86231</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05075</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.82238</v>
       </c>
     </row>
     <row r="6">
@@ -526,16 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>120.50839</v>
+        <v>16.76735</v>
       </c>
       <c r="D6" t="n">
-        <v>85.238</v>
+        <v>16.63027</v>
       </c>
       <c r="E6" t="n">
-        <v>90.35890000000001</v>
+        <v>16.68371</v>
       </c>
       <c r="F6" t="n">
-        <v>511.59416</v>
+        <v>42.52605</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0498</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.80436</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>121.71947</v>
+        <v>16.99157</v>
       </c>
       <c r="D7" t="n">
-        <v>84.94711</v>
+        <v>16.47368</v>
       </c>
       <c r="E7" t="n">
-        <v>91.48824</v>
+        <v>16.52978</v>
       </c>
       <c r="F7" t="n">
-        <v>523.0102000000001</v>
+        <v>42.86099</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05034</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.82254</v>
       </c>
     </row>
     <row r="8">
@@ -564,16 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>122.44832</v>
+        <v>17.16024</v>
       </c>
       <c r="D8" t="n">
-        <v>86.22859</v>
+        <v>16.70814</v>
       </c>
       <c r="E8" t="n">
-        <v>90.47472</v>
+        <v>16.83772</v>
       </c>
       <c r="F8" t="n">
-        <v>520.05786</v>
+        <v>42.76581</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.05147</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.83614</v>
       </c>
     </row>
     <row r="9">
@@ -583,16 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>121.57529</v>
+        <v>17.14109</v>
       </c>
       <c r="D9" t="n">
-        <v>87.00633999999999</v>
+        <v>16.40431</v>
       </c>
       <c r="E9" t="n">
-        <v>90.89004</v>
+        <v>16.55957</v>
       </c>
       <c r="F9" t="n">
-        <v>512.62923</v>
+        <v>43.08485</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.04965</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.81479</v>
       </c>
     </row>
     <row r="10">
@@ -602,27 +660,53 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>119.63435</v>
+        <v>16.98282</v>
       </c>
       <c r="D10" t="n">
-        <v>85.46259000000001</v>
+        <v>16.53077</v>
       </c>
       <c r="E10" t="n">
-        <v>89.98538000000001</v>
+        <v>16.89185</v>
       </c>
       <c r="F10" t="n">
-        <v>511.29553</v>
+        <v>42.27202</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.82333</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Height</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Diameter</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -634,14 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Micro Bump 3</t>
+          <t>Pad Pos 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.52815</v>
+        <v>16.88776</v>
       </c>
       <c r="D12" t="n">
-        <v>24.60373</v>
+        <v>16.7016</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.71174</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43.16277</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.80762</v>
       </c>
     </row>
     <row r="13">
@@ -651,10 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.51882</v>
+        <v>16.79539</v>
       </c>
       <c r="D13" t="n">
-        <v>23.95641</v>
+        <v>16.25129</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.64734</v>
+      </c>
+      <c r="F13" t="n">
+        <v>41.71352</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05014</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.82044</v>
       </c>
     </row>
     <row r="14">
@@ -664,10 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.70635</v>
+        <v>16.67645</v>
       </c>
       <c r="D14" t="n">
-        <v>24.65403</v>
+        <v>16.51174</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.64027</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.01776</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05146</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.83405</v>
       </c>
     </row>
     <row r="15">
@@ -677,10 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.756460000000001</v>
+        <v>16.8169</v>
       </c>
       <c r="D15" t="n">
-        <v>24.46173</v>
+        <v>16.43645</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.8056</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42.154</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05069</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.84311</v>
       </c>
     </row>
     <row r="16">
@@ -690,10 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.665480000000001</v>
+        <v>16.70891</v>
       </c>
       <c r="D16" t="n">
-        <v>24.01586</v>
+        <v>16.38585</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.67452</v>
+      </c>
+      <c r="F16" t="n">
+        <v>43.02242</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05071</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.84935</v>
       </c>
     </row>
     <row r="17">
@@ -703,10 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.53074</v>
+        <v>16.77574</v>
       </c>
       <c r="D17" t="n">
-        <v>24.35746</v>
+        <v>16.57923</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.63879</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.36733</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05014</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.80955</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.606769999999999</v>
+        <v>16.79086</v>
       </c>
       <c r="D18" t="n">
-        <v>24.76119</v>
+        <v>16.59565</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.68383</v>
+      </c>
+      <c r="F18" t="n">
+        <v>41.89689</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05046</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.81722</v>
       </c>
     </row>
     <row r="19">
@@ -729,10 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.65499</v>
+        <v>16.84245</v>
       </c>
       <c r="D19" t="n">
-        <v>24.71125</v>
+        <v>16.60903</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.68229</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.59759</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05055</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.82588</v>
       </c>
     </row>
     <row r="20">
@@ -742,10 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.625629999999999</v>
+        <v>16.77529</v>
       </c>
       <c r="D20" t="n">
-        <v>24.65279</v>
+        <v>16.57465</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.60804</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.71651</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05021</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.80504</v>
       </c>
     </row>
     <row r="21">
@@ -769,16 +961,6 @@
           <t>Radius</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -788,26 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>SR Pad Pos 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.6125</v>
+        <v>15.67138</v>
       </c>
       <c r="D22" t="n">
-        <v>16.51783</v>
+        <v>15.44814</v>
       </c>
       <c r="E22" t="n">
-        <v>16.51778</v>
+        <v>15.56181</v>
       </c>
       <c r="F22" t="n">
-        <v>42.32213</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.05097</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.85464</v>
+        <v>251.24357</v>
       </c>
     </row>
     <row r="23">
@@ -817,22 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.49208</v>
+        <v>15.79286</v>
       </c>
       <c r="D23" t="n">
-        <v>16.91054</v>
+        <v>15.75631</v>
       </c>
       <c r="E23" t="n">
-        <v>16.30589</v>
+        <v>15.76522</v>
       </c>
       <c r="F23" t="n">
-        <v>42.43799</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.05073</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.85468</v>
+        <v>255.03372</v>
       </c>
     </row>
     <row r="24">
@@ -842,22 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.99475</v>
+        <v>15.70371</v>
       </c>
       <c r="D24" t="n">
-        <v>16.53352</v>
+        <v>15.58176</v>
       </c>
       <c r="E24" t="n">
-        <v>16.97334</v>
+        <v>15.65282</v>
       </c>
       <c r="F24" t="n">
-        <v>42.74016</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.04941</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.80326</v>
+        <v>257.33405</v>
       </c>
     </row>
     <row r="25">
@@ -867,22 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.75903</v>
+        <v>15.65328</v>
       </c>
       <c r="D25" t="n">
-        <v>16.7232</v>
+        <v>15.40292</v>
       </c>
       <c r="E25" t="n">
-        <v>16.87394</v>
+        <v>15.47939</v>
       </c>
       <c r="F25" t="n">
-        <v>41.8772</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.0494</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.81482</v>
+        <v>252.76819</v>
       </c>
     </row>
     <row r="26">
@@ -892,22 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>17.07059</v>
+        <v>15.50117</v>
       </c>
       <c r="D26" t="n">
-        <v>17.23669</v>
+        <v>15.43912</v>
       </c>
       <c r="E26" t="n">
-        <v>16.66565</v>
+        <v>15.49748</v>
       </c>
       <c r="F26" t="n">
-        <v>42.23161</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.05037</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.79549</v>
+        <v>257.72405</v>
       </c>
     </row>
     <row r="27">
@@ -917,22 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16.68225</v>
+        <v>15.82507</v>
       </c>
       <c r="D27" t="n">
-        <v>16.54784</v>
+        <v>15.37203</v>
       </c>
       <c r="E27" t="n">
-        <v>16.83887</v>
+        <v>15.53433</v>
       </c>
       <c r="F27" t="n">
-        <v>43.33812</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.05069</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.83744</v>
+        <v>258.25091</v>
       </c>
     </row>
     <row r="28">
@@ -942,22 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.84575</v>
+        <v>15.96766</v>
       </c>
       <c r="D28" t="n">
-        <v>16.57618</v>
+        <v>15.69627</v>
       </c>
       <c r="E28" t="n">
-        <v>16.75351</v>
+        <v>15.75078</v>
       </c>
       <c r="F28" t="n">
-        <v>42.07878</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.04991</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.79509</v>
+        <v>251.56609</v>
       </c>
     </row>
     <row r="29">
@@ -967,22 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.44199</v>
+        <v>15.64407</v>
       </c>
       <c r="D29" t="n">
-        <v>16.714</v>
+        <v>15.55606</v>
       </c>
       <c r="E29" t="n">
-        <v>17.07823</v>
+        <v>15.62937</v>
       </c>
       <c r="F29" t="n">
-        <v>42.48562</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.05039</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.81823</v>
+        <v>259.3735</v>
       </c>
     </row>
     <row r="30">
@@ -992,22 +1126,578 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16.83865</v>
+        <v>15.85638</v>
       </c>
       <c r="D30" t="n">
-        <v>16.51963</v>
+        <v>15.67836</v>
       </c>
       <c r="E30" t="n">
-        <v>16.53366</v>
+        <v>15.78262</v>
       </c>
       <c r="F30" t="n">
-        <v>42.70792</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.05106</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.78387</v>
+        <v>258.23799</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace Pos 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.51243</v>
+      </c>
+      <c r="D32" t="n">
+        <v>15.91352</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.21746</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21.6649</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.45313</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17.00089</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15.69728</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.70432</v>
+      </c>
+      <c r="F33" t="n">
+        <v>21.24707</v>
+      </c>
+      <c r="G33" t="n">
+        <v>34.15248</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.74194</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.27995</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.58524</v>
+      </c>
+      <c r="F34" t="n">
+        <v>21.67504</v>
+      </c>
+      <c r="G34" t="n">
+        <v>34.76964</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.79078</v>
+      </c>
+      <c r="D35" t="n">
+        <v>15.61488</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.22937</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.70597</v>
+      </c>
+      <c r="G35" t="n">
+        <v>34.4661</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.87394</v>
+      </c>
+      <c r="D36" t="n">
+        <v>15.7538</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.00425</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.67698</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.75818</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17.34179</v>
+      </c>
+      <c r="D37" t="n">
+        <v>15.95862</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.28933</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.65731</v>
+      </c>
+      <c r="G37" t="n">
+        <v>33.71527</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.58176</v>
+      </c>
+      <c r="D38" t="n">
+        <v>15.94243</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.53271</v>
+      </c>
+      <c r="F38" t="n">
+        <v>22.18499</v>
+      </c>
+      <c r="G38" t="n">
+        <v>34.26426</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.84322</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.0339</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.37403</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.83033</v>
+      </c>
+      <c r="G39" t="n">
+        <v>33.8634</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.46961</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15.75693</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.0458</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.91165</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.98449</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Via Pos 1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.60694</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.1086</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.60608</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.11581</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.60438</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.10224</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.61011</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.12338</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.59462</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.13455</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.59367</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.10145</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.59956</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.08503</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.60297</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.12665</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.5994</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.09472</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Landing Pad 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>16.69333</v>
+      </c>
+      <c r="D52" t="n">
+        <v>16.38508</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16.64136</v>
+      </c>
+      <c r="F52" t="n">
+        <v>42.49694</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>16.89906</v>
+      </c>
+      <c r="D53" t="n">
+        <v>16.72216</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.74906</v>
+      </c>
+      <c r="F53" t="n">
+        <v>41.45061</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>16.59961</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16.4489</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.59575</v>
+      </c>
+      <c r="F54" t="n">
+        <v>42.56282</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>16.84131</v>
+      </c>
+      <c r="D55" t="n">
+        <v>16.08822</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.73882</v>
+      </c>
+      <c r="F55" t="n">
+        <v>42.83199</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>17.18312</v>
+      </c>
+      <c r="D56" t="n">
+        <v>16.50698</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16.83513</v>
+      </c>
+      <c r="F56" t="n">
+        <v>41.76256</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>16.91223</v>
+      </c>
+      <c r="D57" t="n">
+        <v>16.46297</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16.85561</v>
+      </c>
+      <c r="F57" t="n">
+        <v>43.51477</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>16.81109</v>
+      </c>
+      <c r="D58" t="n">
+        <v>16.69834</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16.73468</v>
+      </c>
+      <c r="F58" t="n">
+        <v>41.75521</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>16.76014</v>
+      </c>
+      <c r="D59" t="n">
+        <v>16.60155</v>
+      </c>
+      <c r="E59" t="n">
+        <v>16.65166</v>
+      </c>
+      <c r="F59" t="n">
+        <v>42.92302</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>16.91119</v>
+      </c>
+      <c r="D60" t="n">
+        <v>16.7538</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16.89822</v>
+      </c>
+      <c r="F60" t="n">
+        <v>42.44931</v>
       </c>
     </row>
   </sheetData>
